--- a/zhul-erp-backend/src/test/resources/document-template/fouwell-quotation-v2.xlsx
+++ b/zhul-erp-backend/src/test/resources/document-template/fouwell-quotation-v2.xlsx
@@ -1502,11 +1502,122 @@
     <row r="2" ht="133" customHeight="1">
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Fuzhou Fouwell Technology Co., Ltd.
-17th Floor, Rongdu International, No. 82 Wusi Road, Fuzhou, Fujian, China
-Tel：                 +86 13385915251
-E-Mail：                info@fouwell.com                        
-Alibaba Website：https://fouwell.en.alibaba.com</t>
+          <r>
+            <rPr>
+              <rFont val="Tahoma Bold"/>
+              <charset val="134"/>
+              <sz val="18"/>
+            </rPr>
+            <t>Fuzhou Fouwell Technology Co., Ltd.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">
+17th Floor, Rongdu International, No. 82 Wusi Road, Fuzhou, Fujian, China</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="18"/>
+            </rPr>
+            <t>
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>Tel</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="宋体-简"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>：</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma Bold"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>                 </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>+86 13385915251
+E-Mail</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="宋体-简"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>：</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma Bold"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>                </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>info@fouwell.com</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma Bold"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>                    </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t xml:space="preserve">    
+Alibaba Website</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="宋体-简"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>：</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Tahoma"/>
+              <charset val="134"/>
+              <sz val="12"/>
+            </rPr>
+            <t>https://fouwell.en.alibaba.com</t>
+          </r>
         </is>
       </c>
     </row>
@@ -1639,7 +1750,11 @@
       </c>
     </row>
     <row r="6" ht="22" customFormat="1" customHeight="1" s="3">
-      <c r="B6" s="14" t="n"/>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>${fee.no}</t>
+        </is>
+      </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
           <t>${fee.name}</t>
